--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_FormulaRule/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_FormulaRule/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R7547c59354734f5a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R19aee533ef67456f"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_FormulaRule/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_FormulaRule/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R19aee533ef67456f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R7922bfb37d9e4f09"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_FormulaRule/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_FormulaRule/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R7922bfb37d9e4f09"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R6621249059744484"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_FormulaRule/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_FormulaRule/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R6621249059744484"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R259062f554734ef4"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_FormulaRule/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_FormulaRule/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R259062f554734ef4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc806ef0f38e94a51"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_FormulaRule/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_FormulaRule/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc806ef0f38e94a51"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R733c63afe1154e26"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_FormulaRule/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_FormulaRule/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R733c63afe1154e26"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re9d358f7215246f4"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_FormulaRule/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_FormulaRule/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re9d358f7215246f4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R43bd63b8c2474087"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_FormulaRule/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_FormulaRule/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R43bd63b8c2474087"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd2f3dbcc57664abe"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_FormulaRule/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_FormulaRule/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd2f3dbcc57664abe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8349cbb25ede42ea"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_FormulaRule/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_FormulaRule/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8349cbb25ede42ea"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R2e6f904386be4afe"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_FormulaRule/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_FormulaRule/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R2e6f904386be4afe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Raeb542e8d4d34a31"/>
   </x:sheets>
 </x:workbook>
 </file>
